--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487022_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487022_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1275</v>
+        <v>6.1111</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6756</v>
+        <v>4.8073</v>
       </c>
       <c r="F2" t="n">
-        <v>1.452</v>
+        <v>1.3038</v>
       </c>
       <c r="G2" t="n">
         <v>5.2038</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0756</v>
+        <v>0.0592</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.651</v>
+        <v>-0.5192</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7266</v>
+        <v>0.5784</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5893</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8171</v>
+        <v>6.0172</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0459</v>
+        <v>5.2164</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7712</v>
+        <v>0.8008</v>
       </c>
       <c r="G3" t="n">
         <v>5.3826</v>
@@ -688,13 +688,13 @@
         <v>2.6694</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4218</v>
+        <v>-0.2217</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5192</v>
+        <v>-0.3488</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0974</v>
+        <v>0.1271</v>
       </c>
       <c r="V3" t="n">
         <v>0.2402</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0874</v>
+        <v>5.1726</v>
       </c>
       <c r="E4" t="n">
-        <v>5.298</v>
+        <v>4.9463</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2106</v>
+        <v>0.2263</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1067</v>
+        <v>2.2088</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3907</v>
+        <v>0.5091</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2839</v>
+        <v>1.6997</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6894</v>
+        <v>3.76</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8606</v>
+        <v>1.366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8288</v>
+        <v>2.394</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5827</v>
+        <v>-1.5512</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.47</v>
+        <v>-0.8569</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1127</v>
+        <v>-0.6943</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0895</v>
+        <v>0.3129</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9413</v>
+        <v>-0.2326</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1482</v>
+        <v>0.5455</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1088</v>
+        <v>1.4189</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7207</v>
+        <v>1.4189</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5928</v>
+        <v>4.0605</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3962</v>
+        <v>4.775</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1967</v>
+        <v>-0.7145</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2088</v>
+        <v>3.1067</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5091</v>
+        <v>3.3907</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6997</v>
+        <v>-0.2839</v>
       </c>
       <c r="J5" t="n">
-        <v>3.76</v>
+        <v>5.6894</v>
       </c>
       <c r="K5" t="n">
-        <v>1.366</v>
+        <v>4.8606</v>
       </c>
       <c r="L5" t="n">
-        <v>2.394</v>
+        <v>0.8288</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5512</v>
+        <v>-2.5827</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8569</v>
+        <v>-1.47</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6943</v>
+        <v>-1.1127</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2321</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2669</v>
+        <v>1.0626</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7827</v>
+        <v>0.4183</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5158</v>
+        <v>0.6443</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4189</v>
+        <v>-0.1088</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4189</v>
+        <v>0.7207</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.087</v>
+        <v>2.9419</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6245</v>
+        <v>4.272</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5376</v>
+        <v>-1.3301</v>
       </c>
       <c r="G6" t="n">
         <v>0.9065</v>
@@ -922,13 +922,13 @@
         <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5645</v>
+        <v>0.4194</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4493</v>
+        <v>0.0968</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1152</v>
+        <v>0.3226</v>
       </c>
       <c r="V6" t="n">
         <v>0.5893</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7253</v>
+        <v>1.7755</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0245</v>
+        <v>0.9857</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7009</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>1.8714</v>
@@ -1000,13 +1000,13 @@
         <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0593</v>
+        <v>0.1095</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4416</v>
+        <v>0.4029</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3823</v>
+        <v>-0.2934</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8451</v>
+        <v>1.141</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8024</v>
+        <v>0.8633</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0427</v>
+        <v>0.2777</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0498</v>
+        <v>2.3217</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6813</v>
+        <v>-0.2045</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6315</v>
+        <v>2.5262</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7288</v>
+        <v>4.0017</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0973</v>
+        <v>1.9889</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6315</v>
+        <v>2.0128</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7786</v>
+        <v>-1.68</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7786</v>
+        <v>-2.1934</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.5134</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8214</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0736</v>
+        <v>0.2567</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0736</v>
+        <v>-0.0582</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.3149</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7351</v>
+        <v>0.9497</v>
       </c>
       <c r="E9" t="n">
-        <v>0.902</v>
+        <v>0.907</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.167</v>
+        <v>0.0427</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3217</v>
+        <v>-0.0498</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2045</v>
+        <v>-0.6813</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5262</v>
+        <v>0.6315</v>
       </c>
       <c r="J9" t="n">
-        <v>4.0017</v>
+        <v>0.7288</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9889</v>
+        <v>0.0973</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0128</v>
+        <v>0.6315</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.68</v>
+        <v>-0.7786</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1934</v>
+        <v>-0.7786</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5134</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1492</v>
+        <v>0.1782</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0195</v>
+        <v>0.1782</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1297</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8758</v>
+        <v>-1.9581</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8708</v>
+        <v>-1.8049</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.005</v>
+        <v>-0.1532</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0642</v>
@@ -1234,13 +1234,13 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1956</v>
+        <v>-0.2779</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2635</v>
+        <v>-0.1976</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0679</v>
+        <v>-0.0803</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2951</v>
+        <v>-2.1016</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2049</v>
+        <v>-1.1003</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0903</v>
+        <v>-1.0013</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1301</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1383</v>
+        <v>0.0552</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1976</v>
+        <v>-0.093</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0593</v>
+        <v>0.1482</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6435</v>
+        <v>-4.2482</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7297</v>
+        <v>-3.2454</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9139</v>
+        <v>-1.0028</v>
       </c>
       <c r="G12" t="n">
         <v>-5.2469</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0825</v>
+        <v>0.3129</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5192</v>
+        <v>-0.035</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4368</v>
+        <v>0.3479</v>
       </c>
       <c r="V12" t="n">
         <v>0.4805</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.2029</v>
+        <v>19.8616</v>
       </c>
       <c r="E13" t="n">
-        <v>19.9637</v>
+        <v>20.6224</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7609000000000002</v>
+        <v>-0.7607999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>13.5105</v>
@@ -1468,10 +1468,10 @@
         <v>15.4007</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6082</v>
+        <v>2.267</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0469</v>
+        <v>-0.3882000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>2.6552</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.028</v>
+        <v>2.2821</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1454</v>
+        <v>1.7021</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1175</v>
+        <v>0.58</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0624</v>
+        <v>2.256</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1754</v>
+        <v>0.6486</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.113</v>
+        <v>1.6074</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4878</v>
+        <v>3.0078</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3694</v>
+        <v>1.2847</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1184</v>
+        <v>1.7231</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4255</v>
+        <v>-0.7519</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.194</v>
+        <v>-0.6362</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2314</v>
+        <v>-0.1157</v>
       </c>
       <c r="P14" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.4374</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-0.2053</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.6427</v>
-      </c>
       <c r="S14" t="n">
-        <v>2.1175</v>
+        <v>-0.3846</v>
       </c>
       <c r="T14" t="n">
-        <v>2.212</v>
+        <v>-0.279</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0945</v>
+        <v>-0.1055</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7077</v>
+        <v>1.6368</v>
       </c>
       <c r="E15" t="n">
-        <v>2.696</v>
+        <v>1.5764</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9883</v>
+        <v>0.0604</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2088</v>
+        <v>0.0624</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0034</v>
+        <v>0.1754</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2054</v>
+        <v>-0.113</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7891</v>
+        <v>1.4878</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4473</v>
+        <v>1.3694</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3418</v>
+        <v>0.1184</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5804</v>
+        <v>-1.4255</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4439</v>
+        <v>-1.194</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1365</v>
+        <v>-0.2314</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6776</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1122</v>
+        <v>0.643</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5654</v>
+        <v>0.0834</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6806</v>
+        <v>1.3643</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3883</v>
+        <v>2.3822</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2923</v>
+        <v>-1.0179</v>
       </c>
       <c r="G16" t="n">
-        <v>2.256</v>
+        <v>0.2088</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6486</v>
+        <v>0.0034</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6074</v>
+        <v>0.2054</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0078</v>
+        <v>2.7891</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2847</v>
+        <v>1.4473</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7231</v>
+        <v>1.3418</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7519</v>
+        <v>-2.5804</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6362</v>
+        <v>-1.4439</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1157</v>
+        <v>-1.1365</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.986</v>
+        <v>0.3341</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5928</v>
+        <v>-0.2016</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3932</v>
+        <v>0.5357</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4592</v>
+        <v>0.569</v>
       </c>
       <c r="E17" t="n">
         <v>3.0806</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6214</v>
+        <v>-2.5116</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6381</v>
@@ -1780,13 +1780,13 @@
         <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6358</v>
+        <v>-0.526</v>
       </c>
       <c r="T17" t="n">
         <v>-0.527</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1088</v>
+        <v>0.001</v>
       </c>
       <c r="V17" t="n">
         <v>1.5277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2638</v>
+        <v>-0.2551</v>
       </c>
       <c r="E18" t="n">
-        <v>4.3762</v>
+        <v>3.9577</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.64</v>
+        <v>-4.2128</v>
       </c>
       <c r="G18" t="n">
         <v>0.2379</v>
@@ -1858,13 +1858,13 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2964</v>
+        <v>-0.2877</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0931</v>
+        <v>-0.5115</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2033</v>
+        <v>0.2238</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7946</v>
+        <v>-0.3867</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7541</v>
+        <v>-1.5449</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9594</v>
+        <v>1.1582</v>
       </c>
       <c r="G19" t="n">
         <v>0.8822</v>
@@ -1936,13 +1936,13 @@
         <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4448</v>
+        <v>-0.0368</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4611</v>
+        <v>-0.2519</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0163</v>
+        <v>0.2151</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.599</v>
+        <v>-2.0272</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5692</v>
+        <v>2.8831</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.1683</v>
+        <v>-4.9102</v>
       </c>
       <c r="G20" t="n">
         <v>1.7978</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7191</v>
+        <v>-0.1473</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.775</v>
+        <v>-0.4612</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0559</v>
+        <v>0.3139</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4189</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6813</v>
+        <v>-2.6447</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4521</v>
+        <v>-2.3475</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2291</v>
+        <v>-0.2972</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3927</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1756</v>
+        <v>0.2122</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2414</v>
+        <v>0.1734</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4055</v>
+        <v>-3.2644</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1206</v>
+        <v>-0.9114</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2849</v>
+        <v>-2.3529</v>
       </c>
       <c r="G22" t="n">
         <v>-4.504</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2855</v>
+        <v>-0.1443</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7827</v>
+        <v>-0.5735</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4972</v>
+        <v>0.4292</v>
       </c>
       <c r="V22" t="n">
         <v>1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1215</v>
+        <v>-3.5043</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3091</v>
+        <v>-2.8907</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8124</v>
+        <v>-0.6137</v>
       </c>
       <c r="G23" t="n">
         <v>-2.436</v>
@@ -2248,13 +2248,13 @@
         <v>1.6427</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6424</v>
+        <v>-0.0252</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5192</v>
+        <v>-0.1008</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1231</v>
+        <v>0.0756</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6591</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3102</v>
+        <v>-5.1149</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.353</v>
+        <v>-4.0392</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9571</v>
+        <v>-1.0757</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9483</v>
@@ -2326,13 +2326,13 @@
         <v>1.0267</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0868</v>
+        <v>0.1085</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4534</v>
+        <v>-0.1396</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3666</v>
+        <v>0.248</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0698</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9024</v>
+        <v>-6.4631</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5059</v>
+        <v>-3.0875</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3965</v>
+        <v>-3.3756</v>
       </c>
       <c r="G25" t="n">
         <v>-7.0364</v>
@@ -2404,13 +2404,13 @@
         <v>1.6427</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.482</v>
+        <v>-0.0427</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7091</v>
+        <v>-0.2907</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2271</v>
+        <v>0.248</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-19.2028</v>
+        <v>-17.8082</v>
       </c>
       <c r="E26" t="n">
         <v>0.7608999999999981</v>
       </c>
       <c r="F26" t="n">
-        <v>-19.9638</v>
+        <v>-18.569</v>
       </c>
       <c r="G26" t="n">
         <v>-13.5104</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.142200000000001</v>
+        <v>-5.1422</v>
       </c>
       <c r="I26" t="n">
         <v>-8.3682</v>
@@ -2482,13 +2482,13 @@
         <v>13.3472</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.6081</v>
+        <v>-0.2135000000000001</v>
       </c>
       <c r="T26" t="n">
         <v>-2.6551</v>
       </c>
       <c r="U26" t="n">
-        <v>1.047</v>
+        <v>2.4416</v>
       </c>
       <c r="V26" t="n">
         <v>-2.0308</v>
